--- a/backend/data/financials_by_company/000534.SZ.xlsx
+++ b/backend/data/financials_by_company/000534.SZ.xlsx
@@ -687,644 +687,644 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>1040753.028425</v>
+        <v>5922241.513006</v>
       </c>
       <c r="C2" t="n">
-        <v>0.170509</v>
+        <v>0.255635</v>
       </c>
       <c r="D2" t="n">
-        <v>345635074.94</v>
+        <v>179743886.07</v>
       </c>
       <c r="E2" t="n">
-        <v>6103818.85</v>
+        <v>23166794.66</v>
       </c>
       <c r="F2" t="n">
-        <v>6103818.85</v>
+        <v>23166794.66</v>
       </c>
       <c r="G2" t="n">
-        <v>192740650.65</v>
+        <v>95292383.72</v>
       </c>
       <c r="H2" t="n">
-        <v>88238337.98</v>
+        <v>62115225.17</v>
       </c>
       <c r="I2" t="n">
-        <v>269315581.85</v>
+        <v>135475510.41</v>
       </c>
       <c r="J2" t="n">
-        <v>351738893.79</v>
+        <v>202910680.73</v>
       </c>
       <c r="K2" t="n">
-        <v>263500555.81</v>
+        <v>140795455.56</v>
       </c>
       <c r="L2" t="n">
-        <v>-38272523.37</v>
+        <v>-18535205.27</v>
       </c>
       <c r="M2" t="n">
-        <v>38532994.55</v>
+        <v>21404001.21</v>
       </c>
       <c r="N2" t="n">
-        <v>2579955.4</v>
+        <v>3414834.95</v>
       </c>
       <c r="O2" t="n">
-        <v>187677584.828425</v>
+        <v>78047830.573006</v>
       </c>
       <c r="P2" t="n">
-        <v>192740650.65</v>
+        <v>95292383.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>824152306.13</v>
+        <v>584990275.53</v>
       </c>
       <c r="R2" t="n">
-        <v>2130537.08</v>
+        <v>4591183.68</v>
       </c>
       <c r="S2" t="n">
-        <v>223466254.93</v>
+        <v>119178577.06</v>
       </c>
       <c r="T2" t="n">
-        <v>510436045</v>
+        <v>502596961</v>
       </c>
       <c r="U2" t="n">
-        <v>490184768</v>
+        <v>494768347</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3776</v>
+        <v>0.1896</v>
       </c>
       <c r="W2" t="n">
-        <v>0.3932</v>
+        <v>0.1926</v>
       </c>
       <c r="X2" t="n">
-        <v>192740650.65</v>
+        <v>95292383.72</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>192740650.65</v>
+        <v>95292383.72</v>
       </c>
       <c r="AA2" t="n">
-        <v>6131971.99</v>
+        <v>6421553.29</v>
       </c>
       <c r="AB2" t="n">
-        <v>186608678.66</v>
+        <v>88870830.43000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>186608678.66</v>
+        <v>88870830.43000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>38358882.6</v>
+        <v>30520623.92</v>
       </c>
       <c r="AE2" t="n">
-        <v>224967561.26</v>
+        <v>119391454.35</v>
       </c>
       <c r="AF2" t="n">
-        <v>1501306.33</v>
+        <v>212877.29</v>
       </c>
       <c r="AG2" t="n">
-        <v>6104885.91</v>
+        <v>23166794.66</v>
       </c>
       <c r="AH2" t="n">
-        <v>-4624040.06</v>
+        <v>-63791.03</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1480845.85</v>
+        <v>-23103003.63</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-38272523.37</v>
+        <v>-18535205.27</v>
       </c>
       <c r="AK2" t="n">
-        <v>2319484.22</v>
+        <v>546039.01</v>
       </c>
       <c r="AL2" t="n">
-        <v>38532994.55</v>
+        <v>21404001.21</v>
       </c>
       <c r="AM2" t="n">
-        <v>2579955.4</v>
+        <v>3414834.95</v>
       </c>
       <c r="AN2" t="n">
-        <v>254712758.62</v>
+        <v>71265274.27</v>
       </c>
       <c r="AO2" t="n">
-        <v>554836724.28</v>
+        <v>449514765.12</v>
       </c>
       <c r="AP2" t="n">
-        <v>12471662</v>
+        <v>6864127.48</v>
       </c>
       <c r="AQ2" t="n">
-        <v>18797545.58</v>
+        <v>16572949.22</v>
       </c>
       <c r="AR2" t="n">
-        <v>18797545.58</v>
+        <v>16572949.22</v>
       </c>
       <c r="AS2" t="n">
-        <v>172790442.12</v>
+        <v>76715959.3</v>
       </c>
       <c r="AT2" t="n">
-        <v>303017721.76</v>
+        <v>292455697.94</v>
       </c>
       <c r="AU2" t="n">
-        <v>245808791.66</v>
+        <v>242574643.45</v>
       </c>
       <c r="AV2" t="n">
-        <v>57208930.1</v>
+        <v>49881054.49</v>
       </c>
       <c r="AW2" t="n">
-        <v>2130537.08</v>
+        <v>4591183.68</v>
       </c>
       <c r="AX2" t="n">
-        <v>809549482.9</v>
+        <v>520780039.39</v>
       </c>
       <c r="AY2" t="n">
-        <v>269315581.85</v>
+        <v>135475510.41</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1078865064.75</v>
+        <v>656255549.8</v>
       </c>
       <c r="BA2" t="n">
-        <v>1078865064.75</v>
+        <v>656255549.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>3907305.735875</v>
+        <v>-995373.2602660001</v>
       </c>
       <c r="C3" t="n">
-        <v>0.226813</v>
+        <v>0.212254</v>
       </c>
       <c r="D3" t="n">
-        <v>322442576.91</v>
+        <v>223430321.84</v>
       </c>
       <c r="E3" t="n">
-        <v>17226984.7</v>
+        <v>-4689539.11</v>
       </c>
       <c r="F3" t="n">
-        <v>17226984.7</v>
+        <v>-4689539.11</v>
       </c>
       <c r="G3" t="n">
-        <v>176554971.16</v>
+        <v>101737836.78</v>
       </c>
       <c r="H3" t="n">
-        <v>71550940.91</v>
+        <v>63158370.94</v>
       </c>
       <c r="I3" t="n">
-        <v>252877531.34</v>
+        <v>183774269.01</v>
       </c>
       <c r="J3" t="n">
-        <v>339669561.61</v>
+        <v>218740782.73</v>
       </c>
       <c r="K3" t="n">
-        <v>268118620.7</v>
+        <v>155582411.79</v>
       </c>
       <c r="L3" t="n">
-        <v>-23353542.32</v>
+        <v>-20292685.05</v>
       </c>
       <c r="M3" t="n">
-        <v>23910658.47</v>
+        <v>21554354.78</v>
       </c>
       <c r="N3" t="n">
-        <v>2142659.96</v>
+        <v>1767905.11</v>
       </c>
       <c r="O3" t="n">
-        <v>163235292.195875</v>
+        <v>105432002.629734</v>
       </c>
       <c r="P3" t="n">
-        <v>176554971.16</v>
+        <v>101737836.78</v>
       </c>
       <c r="Q3" t="n">
-        <v>733154518.58</v>
+        <v>635259720.6900001</v>
       </c>
       <c r="R3" t="n">
-        <v>5958223.77</v>
+        <v>5275072.28</v>
       </c>
       <c r="S3" t="n">
-        <v>243956083.74</v>
+        <v>134768909.37</v>
       </c>
       <c r="T3" t="n">
-        <v>506323405</v>
+        <v>507167681</v>
       </c>
       <c r="U3" t="n">
-        <v>493998241</v>
+        <v>500432055</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3487</v>
+        <v>0.2006</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3574</v>
+        <v>0.2033</v>
       </c>
       <c r="X3" t="n">
-        <v>176554971.16</v>
+        <v>101737836.78</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>176554971.16</v>
+        <v>101737836.78</v>
       </c>
       <c r="AA3" t="n">
-        <v>-12263427.07</v>
+        <v>-3842233.99</v>
       </c>
       <c r="AB3" t="n">
-        <v>188818398.23</v>
+        <v>105580070.77</v>
       </c>
       <c r="AC3" t="n">
-        <v>188818398.23</v>
+        <v>105580070.77</v>
       </c>
       <c r="AD3" t="n">
-        <v>55389564</v>
+        <v>28447986.24</v>
       </c>
       <c r="AE3" t="n">
-        <v>244207962.23</v>
+        <v>134028057.01</v>
       </c>
       <c r="AF3" t="n">
-        <v>251878.49</v>
+        <v>-740852.36</v>
       </c>
       <c r="AG3" t="n">
-        <v>17226984.7</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-27316033.05</v>
-      </c>
+        <v>-4689539.11</v>
+      </c>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>10089048.35</v>
+        <v>4689539.11</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-23353542.32</v>
+        <v>-20292685.05</v>
       </c>
       <c r="AK3" t="n">
-        <v>1585543.81</v>
+        <v>506235.38</v>
       </c>
       <c r="AL3" t="n">
-        <v>23910658.47</v>
+        <v>21554354.78</v>
       </c>
       <c r="AM3" t="n">
-        <v>2142659.96</v>
+        <v>1767905.11</v>
       </c>
       <c r="AN3" t="n">
-        <v>248284844.12</v>
+        <v>158583310.95</v>
       </c>
       <c r="AO3" t="n">
-        <v>480276987.24</v>
+        <v>451485451.68</v>
       </c>
       <c r="AP3" t="n">
-        <v>11427508.71</v>
+        <v>7365709.41</v>
       </c>
       <c r="AQ3" t="n">
-        <v>24355804.73</v>
+        <v>21135183.57</v>
       </c>
       <c r="AR3" t="n">
-        <v>24355804.73</v>
+        <v>21135183.57</v>
       </c>
       <c r="AS3" t="n">
-        <v>105968595.05</v>
+        <v>76375436.92</v>
       </c>
       <c r="AT3" t="n">
-        <v>294901353.74</v>
+        <v>288219152.49</v>
       </c>
       <c r="AU3" t="n">
-        <v>234951745.64</v>
+        <v>235073774.11</v>
       </c>
       <c r="AV3" t="n">
-        <v>59949608.1</v>
+        <v>53145378.38</v>
       </c>
       <c r="AW3" t="n">
-        <v>5958223.77</v>
+        <v>5275072.28</v>
       </c>
       <c r="AX3" t="n">
-        <v>728561831.36</v>
+        <v>610068762.63</v>
       </c>
       <c r="AY3" t="n">
-        <v>252877531.34</v>
+        <v>183774269.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>981439362.7</v>
+        <v>793843031.64</v>
       </c>
       <c r="BA3" t="n">
-        <v>981439362.7</v>
+        <v>793843031.64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-995373.2602660001</v>
+        <v>3907305.735875</v>
       </c>
       <c r="C4" t="n">
-        <v>0.212254</v>
+        <v>0.226813</v>
       </c>
       <c r="D4" t="n">
-        <v>223430321.84</v>
+        <v>322442576.91</v>
       </c>
       <c r="E4" t="n">
-        <v>-4689539.11</v>
+        <v>17226984.7</v>
       </c>
       <c r="F4" t="n">
-        <v>-4689539.11</v>
+        <v>17226984.7</v>
       </c>
       <c r="G4" t="n">
-        <v>101737836.78</v>
+        <v>176554971.16</v>
       </c>
       <c r="H4" t="n">
-        <v>63158370.94</v>
+        <v>71550940.91</v>
       </c>
       <c r="I4" t="n">
-        <v>183774269.01</v>
+        <v>252877531.34</v>
       </c>
       <c r="J4" t="n">
-        <v>218740782.73</v>
+        <v>339669561.61</v>
       </c>
       <c r="K4" t="n">
-        <v>155582411.79</v>
+        <v>268118620.7</v>
       </c>
       <c r="L4" t="n">
-        <v>-20292685.05</v>
+        <v>-23353542.32</v>
       </c>
       <c r="M4" t="n">
-        <v>21554354.78</v>
+        <v>23910658.47</v>
       </c>
       <c r="N4" t="n">
-        <v>1767905.11</v>
+        <v>2142659.96</v>
       </c>
       <c r="O4" t="n">
-        <v>105432002.629734</v>
+        <v>163235292.195875</v>
       </c>
       <c r="P4" t="n">
-        <v>101737836.78</v>
+        <v>176554971.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>635259720.6900001</v>
+        <v>733154518.58</v>
       </c>
       <c r="R4" t="n">
-        <v>5275072.28</v>
+        <v>5958223.77</v>
       </c>
       <c r="S4" t="n">
-        <v>134768909.37</v>
+        <v>243956083.74</v>
       </c>
       <c r="T4" t="n">
-        <v>507167681</v>
+        <v>506323405</v>
       </c>
       <c r="U4" t="n">
-        <v>500432055</v>
+        <v>493998241</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2006</v>
+        <v>0.3487</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2033</v>
+        <v>0.3574</v>
       </c>
       <c r="X4" t="n">
-        <v>101737836.78</v>
+        <v>176554971.16</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>101737836.78</v>
+        <v>176554971.16</v>
       </c>
       <c r="AA4" t="n">
-        <v>-3842233.99</v>
+        <v>-12263427.07</v>
       </c>
       <c r="AB4" t="n">
-        <v>105580070.77</v>
+        <v>188818398.23</v>
       </c>
       <c r="AC4" t="n">
-        <v>105580070.77</v>
+        <v>188818398.23</v>
       </c>
       <c r="AD4" t="n">
-        <v>28447986.24</v>
+        <v>55389564</v>
       </c>
       <c r="AE4" t="n">
-        <v>134028057.01</v>
+        <v>244207962.23</v>
       </c>
       <c r="AF4" t="n">
-        <v>-740852.36</v>
+        <v>251878.49</v>
       </c>
       <c r="AG4" t="n">
-        <v>-4689539.11</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
+        <v>17226984.7</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-27316033.05</v>
+      </c>
       <c r="AI4" t="n">
-        <v>4689539.11</v>
+        <v>10089048.35</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-20292685.05</v>
+        <v>-23353542.32</v>
       </c>
       <c r="AK4" t="n">
-        <v>506235.38</v>
+        <v>1585543.81</v>
       </c>
       <c r="AL4" t="n">
-        <v>21554354.78</v>
+        <v>23910658.47</v>
       </c>
       <c r="AM4" t="n">
-        <v>1767905.11</v>
+        <v>2142659.96</v>
       </c>
       <c r="AN4" t="n">
-        <v>158583310.95</v>
+        <v>248284844.12</v>
       </c>
       <c r="AO4" t="n">
-        <v>451485451.68</v>
+        <v>480276987.24</v>
       </c>
       <c r="AP4" t="n">
-        <v>7365709.41</v>
+        <v>11427508.71</v>
       </c>
       <c r="AQ4" t="n">
-        <v>21135183.57</v>
+        <v>24355804.73</v>
       </c>
       <c r="AR4" t="n">
-        <v>21135183.57</v>
+        <v>24355804.73</v>
       </c>
       <c r="AS4" t="n">
-        <v>76375436.92</v>
+        <v>105968595.05</v>
       </c>
       <c r="AT4" t="n">
-        <v>288219152.49</v>
+        <v>294901353.74</v>
       </c>
       <c r="AU4" t="n">
-        <v>235073774.11</v>
+        <v>234951745.64</v>
       </c>
       <c r="AV4" t="n">
-        <v>53145378.38</v>
+        <v>59949608.1</v>
       </c>
       <c r="AW4" t="n">
-        <v>5275072.28</v>
+        <v>5958223.77</v>
       </c>
       <c r="AX4" t="n">
-        <v>610068762.63</v>
+        <v>728561831.36</v>
       </c>
       <c r="AY4" t="n">
-        <v>183774269.01</v>
+        <v>252877531.34</v>
       </c>
       <c r="AZ4" t="n">
-        <v>793843031.64</v>
+        <v>981439362.7</v>
       </c>
       <c r="BA4" t="n">
-        <v>793843031.64</v>
+        <v>981439362.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>5922241.513006</v>
+        <v>1040753.028425</v>
       </c>
       <c r="C5" t="n">
-        <v>0.255635</v>
+        <v>0.170509</v>
       </c>
       <c r="D5" t="n">
-        <v>179743886.07</v>
+        <v>345635074.94</v>
       </c>
       <c r="E5" t="n">
-        <v>23166794.66</v>
+        <v>6103818.85</v>
       </c>
       <c r="F5" t="n">
-        <v>23166794.66</v>
+        <v>6103818.85</v>
       </c>
       <c r="G5" t="n">
-        <v>95292383.72</v>
+        <v>192740650.65</v>
       </c>
       <c r="H5" t="n">
-        <v>62115225.17</v>
+        <v>88238337.98</v>
       </c>
       <c r="I5" t="n">
-        <v>135475510.41</v>
+        <v>269315581.85</v>
       </c>
       <c r="J5" t="n">
-        <v>202910680.73</v>
+        <v>351738893.79</v>
       </c>
       <c r="K5" t="n">
-        <v>140795455.56</v>
+        <v>263500555.81</v>
       </c>
       <c r="L5" t="n">
-        <v>-18535205.27</v>
+        <v>-38272523.37</v>
       </c>
       <c r="M5" t="n">
-        <v>21404001.21</v>
+        <v>38532994.55</v>
       </c>
       <c r="N5" t="n">
-        <v>3414834.95</v>
+        <v>2579955.4</v>
       </c>
       <c r="O5" t="n">
-        <v>78047830.573006</v>
+        <v>187677584.828425</v>
       </c>
       <c r="P5" t="n">
-        <v>95292383.72</v>
+        <v>192740650.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>584990275.53</v>
+        <v>824152306.13</v>
       </c>
       <c r="R5" t="n">
-        <v>4591183.68</v>
+        <v>2130537.08</v>
       </c>
       <c r="S5" t="n">
-        <v>119178577.06</v>
+        <v>223466254.93</v>
       </c>
       <c r="T5" t="n">
-        <v>502596961</v>
+        <v>510436045</v>
       </c>
       <c r="U5" t="n">
-        <v>494768347</v>
+        <v>490184768</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1896</v>
+        <v>0.3776</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1926</v>
+        <v>0.3932</v>
       </c>
       <c r="X5" t="n">
-        <v>95292383.72</v>
+        <v>192740650.65</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>95292383.72</v>
+        <v>192740650.65</v>
       </c>
       <c r="AA5" t="n">
-        <v>6421553.29</v>
+        <v>6131971.99</v>
       </c>
       <c r="AB5" t="n">
-        <v>88870830.43000001</v>
+        <v>186608678.66</v>
       </c>
       <c r="AC5" t="n">
-        <v>88870830.43000001</v>
+        <v>186608678.66</v>
       </c>
       <c r="AD5" t="n">
-        <v>30520623.92</v>
+        <v>38358882.6</v>
       </c>
       <c r="AE5" t="n">
-        <v>119391454.35</v>
+        <v>224967561.26</v>
       </c>
       <c r="AF5" t="n">
-        <v>212877.29</v>
+        <v>1501306.33</v>
       </c>
       <c r="AG5" t="n">
-        <v>23166794.66</v>
+        <v>6104885.91</v>
       </c>
       <c r="AH5" t="n">
-        <v>-63791.03</v>
+        <v>-4624040.06</v>
       </c>
       <c r="AI5" t="n">
-        <v>-23103003.63</v>
+        <v>-1480845.85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-18535205.27</v>
+        <v>-38272523.37</v>
       </c>
       <c r="AK5" t="n">
-        <v>546039.01</v>
+        <v>2319484.22</v>
       </c>
       <c r="AL5" t="n">
-        <v>21404001.21</v>
+        <v>38532994.55</v>
       </c>
       <c r="AM5" t="n">
-        <v>3414834.95</v>
+        <v>2579955.4</v>
       </c>
       <c r="AN5" t="n">
-        <v>71265274.27</v>
+        <v>254712758.62</v>
       </c>
       <c r="AO5" t="n">
-        <v>449514765.12</v>
+        <v>554836724.28</v>
       </c>
       <c r="AP5" t="n">
-        <v>6864127.48</v>
+        <v>12471662</v>
       </c>
       <c r="AQ5" t="n">
-        <v>16572949.22</v>
+        <v>18797545.58</v>
       </c>
       <c r="AR5" t="n">
-        <v>16572949.22</v>
+        <v>18797545.58</v>
       </c>
       <c r="AS5" t="n">
-        <v>76715959.3</v>
+        <v>172790442.12</v>
       </c>
       <c r="AT5" t="n">
-        <v>292455697.94</v>
+        <v>303017721.76</v>
       </c>
       <c r="AU5" t="n">
-        <v>242574643.45</v>
+        <v>245808791.66</v>
       </c>
       <c r="AV5" t="n">
-        <v>49881054.49</v>
+        <v>57208930.1</v>
       </c>
       <c r="AW5" t="n">
-        <v>4591183.68</v>
+        <v>2130537.08</v>
       </c>
       <c r="AX5" t="n">
-        <v>520780039.39</v>
+        <v>809549482.9</v>
       </c>
       <c r="AY5" t="n">
-        <v>135475510.41</v>
+        <v>269315581.85</v>
       </c>
       <c r="AZ5" t="n">
-        <v>656255549.8</v>
+        <v>1078865064.75</v>
       </c>
       <c r="BA5" t="n">
-        <v>656255549.8</v>
+        <v>1078865064.75</v>
       </c>
     </row>
   </sheetData>
@@ -1695,296 +1695,422 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46022</v>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="n">
+        <v>495713096</v>
+      </c>
+      <c r="C2" t="n">
+        <v>495713096</v>
+      </c>
+      <c r="D2" t="n">
+        <v>101328598.78</v>
+      </c>
+      <c r="E2" t="n">
+        <v>487842662.85</v>
+      </c>
+      <c r="F2" t="n">
+        <v>799966044.39</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1493199587.63</v>
+      </c>
+      <c r="H2" t="n">
+        <v>83748113.73999999</v>
+      </c>
+      <c r="I2" t="n">
+        <v>799966044.39</v>
+      </c>
+      <c r="J2" t="n">
+        <v>8332673.14</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1071171820.88</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1341555858.36</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1099490354.07</v>
+      </c>
+      <c r="N2" t="n">
+        <v>28318533.19</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1071171820.88</v>
+      </c>
+      <c r="P2" t="n">
+        <v>27011800</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>573577248.8</v>
+      </c>
+      <c r="R2" t="n">
+        <v>10085590.82</v>
+      </c>
+      <c r="S2" t="n">
+        <v>495713096</v>
+      </c>
+      <c r="T2" t="n">
+        <v>495713096</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1017964343.14</v>
+      </c>
+      <c r="V2" t="n">
+        <v>438323453.37</v>
+      </c>
       <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="n">
-        <v>-38101934.69</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>527282344.62</v>
-      </c>
-      <c r="BO2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>145169396.58</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>14437346.17</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>278716710.62</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>8332673.14</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>270384037.48</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>579640889.77</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>6736194.89</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>209125952.23</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>151643729.27</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>361383702.78</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>135843334.14</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>439880</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>23562213.19</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>201538275.45</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>2117454697.21</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1454065693.7</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>141759245.2</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>17052799.03</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>10372812.02</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>101504464.96</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>101504464.96</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>9168917.890000001</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>40026662.41</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>271205776.49</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>271205776.49</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>862205346</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>-193842965.66</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1056048311.66</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>224575311.84</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>42661286.52</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>296127768.86</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>492683944.44</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>663389003.51</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>65508737.28</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>7598919.28</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>102004036.62</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>21010254.67</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>25198070.01</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>55795711.94</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>38587030.42</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>128991111.94</v>
+      </c>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="n">
+        <v>320699167.97</v>
+      </c>
       <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="inlineStr"/>
-      <c r="BR2" t="inlineStr"/>
-      <c r="BS2" t="inlineStr"/>
+      <c r="BQ2" t="n">
+        <v>320699167.97</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>320699167.97</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45657</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>510116596</v>
+        <v>500623096</v>
       </c>
       <c r="C3" t="n">
-        <v>510116596</v>
+        <v>500623096</v>
       </c>
       <c r="D3" t="n">
-        <v>1089977828.56</v>
+        <v>330375571.21</v>
       </c>
       <c r="E3" t="n">
-        <v>1627900348.33</v>
+        <v>631771830</v>
       </c>
       <c r="F3" t="n">
-        <v>962327492.7</v>
+        <v>866964062.79</v>
       </c>
       <c r="G3" t="n">
-        <v>2831813537.64</v>
+        <v>1815998330.35</v>
       </c>
       <c r="H3" t="n">
-        <v>245048952.17</v>
+        <v>92741968.29000001</v>
       </c>
       <c r="I3" t="n">
-        <v>962327492.7</v>
+        <v>866964062.79</v>
       </c>
       <c r="J3" t="n">
-        <v>22200514.99</v>
+        <v>3876953.57</v>
       </c>
       <c r="K3" t="n">
-        <v>1360987340.6</v>
+        <v>1192252473.62</v>
       </c>
       <c r="L3" t="n">
-        <v>2459656173.99</v>
+        <v>1620995187.88</v>
       </c>
       <c r="M3" t="n">
-        <v>1549405605.07</v>
+        <v>1240180631.18</v>
       </c>
       <c r="N3" t="n">
-        <v>188418264.47</v>
+        <v>47928157.56</v>
       </c>
       <c r="O3" t="n">
-        <v>1360987340.6</v>
+        <v>1192252473.62</v>
       </c>
       <c r="P3" t="n">
-        <v>479590081.24</v>
+        <v>58534935</v>
       </c>
       <c r="Q3" t="n">
-        <v>937198743.6799999</v>
+        <v>650265211.75</v>
       </c>
       <c r="R3" t="n">
-        <v>257724506.65</v>
+        <v>37062450.42</v>
       </c>
       <c r="S3" t="n">
-        <v>510116596</v>
+        <v>500623096</v>
       </c>
       <c r="T3" t="n">
-        <v>510116596</v>
+        <v>500623096</v>
       </c>
       <c r="U3" t="n">
-        <v>2420875731.14</v>
+        <v>1194624260.3</v>
       </c>
       <c r="V3" t="n">
-        <v>1433001685.12</v>
+        <v>598631488.92</v>
       </c>
       <c r="W3" t="n">
-        <v>206285885.71</v>
+        <v>15654413.9</v>
       </c>
       <c r="X3" t="n">
-        <v>91409104.86</v>
+        <v>135920061.02</v>
       </c>
       <c r="Y3" t="n">
         <v>14437346.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>1120869348.38</v>
+        <v>432619667.83</v>
       </c>
       <c r="AA3" t="n">
-        <v>22200514.99</v>
+        <v>3876953.57</v>
       </c>
       <c r="AB3" t="n">
-        <v>1098668833.39</v>
+        <v>428742714.26</v>
       </c>
       <c r="AC3" t="n">
-        <v>987874046.02</v>
+        <v>595992771.38</v>
       </c>
       <c r="AD3" t="n">
-        <v>44543007.74</v>
+        <v>10444073.59</v>
       </c>
       <c r="AE3" t="n">
-        <v>507030999.95</v>
+        <v>199152162.17</v>
       </c>
       <c r="AF3" t="n">
-        <v>372157363.65</v>
+        <v>195003142.47</v>
       </c>
       <c r="AG3" t="n">
-        <v>433967766.64</v>
+        <v>384862443.26</v>
       </c>
       <c r="AH3" t="n">
-        <v>106803602.55</v>
+        <v>132020557.09</v>
       </c>
       <c r="AI3" t="n">
-        <v>402008</v>
+        <v>529961</v>
       </c>
       <c r="AJ3" t="n">
-        <v>25823444.57</v>
+        <v>26265055.19</v>
       </c>
       <c r="AK3" t="n">
-        <v>300938711.52</v>
+        <v>226046869.98</v>
       </c>
       <c r="AL3" t="n">
-        <v>3970281336.21</v>
+        <v>2434804891.48</v>
       </c>
       <c r="AM3" t="n">
-        <v>2737358338.02</v>
+        <v>1746070151.81</v>
       </c>
       <c r="AN3" t="n">
-        <v>57411561.18</v>
+        <v>179203774.99</v>
       </c>
       <c r="AO3" t="n">
-        <v>45267114.09</v>
+        <v>17462482.77</v>
       </c>
       <c r="AP3" t="n">
-        <v>39405907.67</v>
+        <v>14497518.31</v>
       </c>
       <c r="AQ3" t="n">
-        <v>150608180.8</v>
+        <v>100972294.87</v>
       </c>
       <c r="AR3" t="n">
-        <v>150608180.8</v>
+        <v>100972294.87</v>
       </c>
       <c r="AS3" t="n">
-        <v>10385227.55</v>
+        <v>9624619.380000001</v>
       </c>
       <c r="AT3" t="n">
-        <v>121483934.72</v>
+        <v>90310194.61</v>
       </c>
       <c r="AU3" t="n">
-        <v>398659847.9</v>
+        <v>325288410.83</v>
       </c>
       <c r="AV3" t="n">
-        <v>398659847.9</v>
+        <v>325288410.83</v>
       </c>
       <c r="AW3" t="n">
-        <v>1888075802.67</v>
+        <v>1007648276.47</v>
       </c>
       <c r="AX3" t="n">
-        <v>-319885922.79</v>
+        <v>-233760334.52</v>
       </c>
       <c r="AY3" t="n">
-        <v>2207961725.46</v>
+        <v>1241408610.99</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1094808502</v>
+        <v>288150551.62</v>
       </c>
       <c r="BA3" t="n">
-        <v>61425957.44</v>
+        <v>38185866.35</v>
       </c>
       <c r="BB3" t="n">
-        <v>498425929.63</v>
+        <v>330255767.73</v>
       </c>
       <c r="BC3" t="n">
-        <v>553301336.39</v>
+        <v>584816425.29</v>
       </c>
       <c r="BD3" t="n">
-        <v>1232922998.19</v>
+        <v>688734739.67</v>
       </c>
       <c r="BE3" t="n">
-        <v>58986915.15</v>
+        <v>27744684.82</v>
       </c>
       <c r="BF3" t="n">
-        <v>5071078.16</v>
+        <v>8177995.12</v>
       </c>
       <c r="BG3" t="n">
-        <v>343884908.07</v>
+        <v>118834748.05</v>
       </c>
       <c r="BH3" t="n">
-        <v>87465799.17</v>
+        <v>14310242.78</v>
       </c>
       <c r="BI3" t="n">
-        <v>119214419.58</v>
+        <v>51747227.49</v>
       </c>
       <c r="BJ3" t="n">
-        <v>137204689.32</v>
+        <v>52777277.78</v>
       </c>
       <c r="BK3" t="n">
-        <v>73440136.73999999</v>
+        <v>37510218.23</v>
       </c>
       <c r="BL3" t="n">
-        <v>370485127.99</v>
+        <v>203096807.93</v>
       </c>
       <c r="BM3" t="n">
-        <v>-28948835.24</v>
+        <v>-15631378.92</v>
       </c>
       <c r="BN3" t="n">
-        <v>399433963.23</v>
+        <v>218728186.85</v>
       </c>
       <c r="BO3" t="n">
-        <v>381054832.08</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>206463.6</v>
-      </c>
+        <v>293370285.52</v>
+      </c>
+      <c r="BP3" t="inlineStr"/>
       <c r="BQ3" t="n">
-        <v>380848368.48</v>
+        <v>293370285.52</v>
       </c>
       <c r="BR3" t="n">
-        <v>122732.27</v>
+        <v>5692419.25</v>
       </c>
       <c r="BS3" t="n">
-        <v>380725636.21</v>
+        <v>287677866.27</v>
       </c>
     </row>
     <row r="4">
@@ -2202,423 +2328,297 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44926</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>500623096</v>
+        <v>510116596</v>
       </c>
       <c r="C5" t="n">
-        <v>500623096</v>
+        <v>510116596</v>
       </c>
       <c r="D5" t="n">
-        <v>330375571.21</v>
+        <v>1089977828.56</v>
       </c>
       <c r="E5" t="n">
-        <v>631771830</v>
+        <v>1627900348.33</v>
       </c>
       <c r="F5" t="n">
-        <v>866964062.79</v>
+        <v>962327492.7</v>
       </c>
       <c r="G5" t="n">
-        <v>1815998330.35</v>
+        <v>2831813537.64</v>
       </c>
       <c r="H5" t="n">
-        <v>92741968.29000001</v>
+        <v>245048952.17</v>
       </c>
       <c r="I5" t="n">
-        <v>866964062.79</v>
+        <v>962327492.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3876953.57</v>
+        <v>22200514.99</v>
       </c>
       <c r="K5" t="n">
-        <v>1192252473.62</v>
+        <v>1360987340.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1620995187.88</v>
+        <v>2459656173.99</v>
       </c>
       <c r="M5" t="n">
-        <v>1240180631.18</v>
+        <v>1549405605.07</v>
       </c>
       <c r="N5" t="n">
-        <v>47928157.56</v>
+        <v>188418264.47</v>
       </c>
       <c r="O5" t="n">
-        <v>1192252473.62</v>
+        <v>1360987340.6</v>
       </c>
       <c r="P5" t="n">
-        <v>58534935</v>
+        <v>479590081.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>650265211.75</v>
+        <v>937198743.6799999</v>
       </c>
       <c r="R5" t="n">
-        <v>37062450.42</v>
+        <v>257724506.65</v>
       </c>
       <c r="S5" t="n">
-        <v>500623096</v>
+        <v>510116596</v>
       </c>
       <c r="T5" t="n">
-        <v>500623096</v>
+        <v>510116596</v>
       </c>
       <c r="U5" t="n">
-        <v>1194624260.3</v>
+        <v>2420875731.14</v>
       </c>
       <c r="V5" t="n">
-        <v>598631488.92</v>
+        <v>1433001685.12</v>
       </c>
       <c r="W5" t="n">
-        <v>15654413.9</v>
+        <v>206285885.71</v>
       </c>
       <c r="X5" t="n">
-        <v>135920061.02</v>
+        <v>91409104.86</v>
       </c>
       <c r="Y5" t="n">
         <v>14437346.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>432619667.83</v>
+        <v>1120869348.38</v>
       </c>
       <c r="AA5" t="n">
-        <v>3876953.57</v>
+        <v>22200514.99</v>
       </c>
       <c r="AB5" t="n">
-        <v>428742714.26</v>
+        <v>1098668833.39</v>
       </c>
       <c r="AC5" t="n">
-        <v>595992771.38</v>
+        <v>987874046.02</v>
       </c>
       <c r="AD5" t="n">
-        <v>10444073.59</v>
+        <v>44543007.74</v>
       </c>
       <c r="AE5" t="n">
-        <v>199152162.17</v>
+        <v>507030999.95</v>
       </c>
       <c r="AF5" t="n">
-        <v>195003142.47</v>
+        <v>372157363.65</v>
       </c>
       <c r="AG5" t="n">
-        <v>384862443.26</v>
+        <v>433967766.64</v>
       </c>
       <c r="AH5" t="n">
-        <v>132020557.09</v>
+        <v>106803602.55</v>
       </c>
       <c r="AI5" t="n">
-        <v>529961</v>
+        <v>402008</v>
       </c>
       <c r="AJ5" t="n">
-        <v>26265055.19</v>
+        <v>25823444.57</v>
       </c>
       <c r="AK5" t="n">
-        <v>226046869.98</v>
+        <v>300938711.52</v>
       </c>
       <c r="AL5" t="n">
-        <v>2434804891.48</v>
+        <v>3970281336.21</v>
       </c>
       <c r="AM5" t="n">
-        <v>1746070151.81</v>
+        <v>2737358338.02</v>
       </c>
       <c r="AN5" t="n">
-        <v>179203774.99</v>
+        <v>57411561.18</v>
       </c>
       <c r="AO5" t="n">
-        <v>17462482.77</v>
+        <v>45267114.09</v>
       </c>
       <c r="AP5" t="n">
-        <v>14497518.31</v>
+        <v>39405907.67</v>
       </c>
       <c r="AQ5" t="n">
-        <v>100972294.87</v>
+        <v>150608180.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>100972294.87</v>
+        <v>150608180.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>9624619.380000001</v>
+        <v>10385227.55</v>
       </c>
       <c r="AT5" t="n">
-        <v>90310194.61</v>
+        <v>121483934.72</v>
       </c>
       <c r="AU5" t="n">
-        <v>325288410.83</v>
+        <v>398659847.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>325288410.83</v>
+        <v>398659847.9</v>
       </c>
       <c r="AW5" t="n">
-        <v>1007648276.47</v>
+        <v>1888075802.67</v>
       </c>
       <c r="AX5" t="n">
-        <v>-233760334.52</v>
+        <v>-319885922.79</v>
       </c>
       <c r="AY5" t="n">
-        <v>1241408610.99</v>
+        <v>2207961725.46</v>
       </c>
       <c r="AZ5" t="n">
-        <v>288150551.62</v>
+        <v>1094808502</v>
       </c>
       <c r="BA5" t="n">
-        <v>38185866.35</v>
+        <v>61425957.44</v>
       </c>
       <c r="BB5" t="n">
-        <v>330255767.73</v>
+        <v>498425929.63</v>
       </c>
       <c r="BC5" t="n">
-        <v>584816425.29</v>
+        <v>553301336.39</v>
       </c>
       <c r="BD5" t="n">
-        <v>688734739.67</v>
+        <v>1232922998.19</v>
       </c>
       <c r="BE5" t="n">
-        <v>27744684.82</v>
+        <v>58986915.15</v>
       </c>
       <c r="BF5" t="n">
-        <v>8177995.12</v>
+        <v>5071078.16</v>
       </c>
       <c r="BG5" t="n">
-        <v>118834748.05</v>
+        <v>343884908.07</v>
       </c>
       <c r="BH5" t="n">
-        <v>14310242.78</v>
+        <v>87465799.17</v>
       </c>
       <c r="BI5" t="n">
-        <v>51747227.49</v>
+        <v>119214419.58</v>
       </c>
       <c r="BJ5" t="n">
-        <v>52777277.78</v>
+        <v>137204689.32</v>
       </c>
       <c r="BK5" t="n">
-        <v>37510218.23</v>
+        <v>73440136.73999999</v>
       </c>
       <c r="BL5" t="n">
-        <v>203096807.93</v>
+        <v>370485127.99</v>
       </c>
       <c r="BM5" t="n">
-        <v>-15631378.92</v>
+        <v>-28948835.24</v>
       </c>
       <c r="BN5" t="n">
-        <v>218728186.85</v>
+        <v>399433963.23</v>
       </c>
       <c r="BO5" t="n">
-        <v>293370285.52</v>
-      </c>
-      <c r="BP5" t="inlineStr"/>
+        <v>381054832.08</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>206463.6</v>
+      </c>
       <c r="BQ5" t="n">
-        <v>293370285.52</v>
+        <v>380848368.48</v>
       </c>
       <c r="BR5" t="n">
-        <v>5692419.25</v>
+        <v>122732.27</v>
       </c>
       <c r="BS5" t="n">
-        <v>287677866.27</v>
+        <v>380725636.21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B6" t="n">
-        <v>495713096</v>
-      </c>
-      <c r="C6" t="n">
-        <v>495713096</v>
-      </c>
-      <c r="D6" t="n">
-        <v>101328598.78</v>
-      </c>
-      <c r="E6" t="n">
-        <v>487842662.85</v>
-      </c>
-      <c r="F6" t="n">
-        <v>799966044.39</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1493199587.63</v>
-      </c>
-      <c r="H6" t="n">
-        <v>83748113.73999999</v>
-      </c>
-      <c r="I6" t="n">
-        <v>799966044.39</v>
-      </c>
-      <c r="J6" t="n">
-        <v>8332673.14</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1071171820.88</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1341555858.36</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1099490354.07</v>
-      </c>
-      <c r="N6" t="n">
-        <v>28318533.19</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1071171820.88</v>
-      </c>
-      <c r="P6" t="n">
-        <v>27011800</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>573577248.8</v>
-      </c>
-      <c r="R6" t="n">
-        <v>10085590.82</v>
-      </c>
-      <c r="S6" t="n">
-        <v>495713096</v>
-      </c>
-      <c r="T6" t="n">
-        <v>495713096</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1017964343.14</v>
-      </c>
-      <c r="V6" t="n">
-        <v>438323453.37</v>
-      </c>
+        <v>46022</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
-      <c r="X6" t="n">
-        <v>145169396.58</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>14437346.17</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>278716710.62</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>8332673.14</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>270384037.48</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>579640889.77</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>6736194.89</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>209125952.23</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>151643729.27</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>361383702.78</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>135843334.14</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>439880</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>23562213.19</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>201538275.45</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>2117454697.21</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1454065693.7</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>141759245.2</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>17052799.03</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>10372812.02</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>101504464.96</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>101504464.96</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>9168917.890000001</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>40026662.41</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>271205776.49</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>271205776.49</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>862205346</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>-193842965.66</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1056048311.66</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>224575311.84</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>42661286.52</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>296127768.86</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>492683944.44</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>663389003.51</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>65508737.28</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>7598919.28</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>102004036.62</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>21010254.67</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>25198070.01</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>55795711.94</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>38587030.42</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>128991111.94</v>
-      </c>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
-      <c r="BO6" t="n">
-        <v>320699167.97</v>
-      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="n">
+        <v>-38101934.69</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>527282344.62</v>
+      </c>
+      <c r="BO6" t="inlineStr"/>
       <c r="BP6" t="inlineStr"/>
-      <c r="BQ6" t="n">
-        <v>320699167.97</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>320699167.97</v>
-      </c>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2873,568 +2873,568 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-472532455.02</v>
+        <v>-80028707.15000001</v>
       </c>
       <c r="C2" t="n">
-        <v>-274075297.9</v>
+        <v>-241501602.83</v>
       </c>
       <c r="D2" t="n">
-        <v>850121529.92</v>
+        <v>161326781.35</v>
       </c>
       <c r="E2" t="n">
-        <v>-586789201.77</v>
+        <v>-216696445.88</v>
       </c>
       <c r="F2" t="n">
-        <v>380726679.72</v>
+        <v>316699165.19</v>
       </c>
       <c r="G2" t="n">
-        <v>258038745.01</v>
+        <v>385433489.63</v>
       </c>
       <c r="H2" t="n">
-        <v>360502.47</v>
+        <v>-495196.68</v>
       </c>
       <c r="I2" t="n">
-        <v>122327432.24</v>
+        <v>-68239127.76000001</v>
       </c>
       <c r="J2" t="n">
-        <v>469302284.68</v>
+        <v>-128693872.96</v>
       </c>
       <c r="K2" t="n">
-        <v>11335006.62</v>
+        <v>14068062.1</v>
       </c>
       <c r="L2" t="n">
-        <v>-118078953.96</v>
+        <v>-62587113.58</v>
       </c>
       <c r="M2" t="n">
-        <v>576046232.02</v>
+        <v>-80174821.48</v>
       </c>
       <c r="N2" t="n">
-        <v>576046232.02</v>
+        <v>-80174821.48</v>
       </c>
       <c r="O2" t="n">
-        <v>-274075297.9</v>
+        <v>-241501602.83</v>
       </c>
       <c r="P2" t="n">
-        <v>850121529.92</v>
+        <v>161326781.35</v>
       </c>
       <c r="Q2" t="n">
-        <v>-461231599.19</v>
+        <v>-76212993.53</v>
       </c>
       <c r="R2" t="n">
-        <v>6408142.83</v>
+        <v>-87650000</v>
       </c>
       <c r="S2" t="n">
-        <v>233348.11</v>
+        <v>228070452.35</v>
       </c>
       <c r="T2" t="n">
-        <v>326940878.77</v>
+        <v>318070453.35</v>
       </c>
       <c r="U2" t="n">
-        <v>-326707530.66</v>
-      </c>
-      <c r="V2" t="n">
-        <v>506424.64</v>
-      </c>
-      <c r="W2" t="n">
-        <v>506424.64</v>
-      </c>
+        <v>-90000001</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>-468379514.77</v>
+        <v>-216633445.88</v>
       </c>
       <c r="Y2" t="n">
-        <v>118409687</v>
+        <v>63000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-586789201.77</v>
+        <v>-216696445.88</v>
       </c>
       <c r="AA2" t="n">
-        <v>114256746.75</v>
+        <v>136667738.73</v>
       </c>
       <c r="AB2" t="n">
-        <v>-237771444.09</v>
+        <v>10035231.99</v>
       </c>
       <c r="AC2" t="n">
-        <v>-21975798.81</v>
+        <v>-6957024.73</v>
       </c>
       <c r="AD2" t="n">
-        <v>-16720146.87</v>
+        <v>-55839520.98</v>
       </c>
       <c r="AE2" t="n">
-        <v>-127830713.88</v>
+        <v>-58549708.66</v>
       </c>
       <c r="AF2" t="n">
-        <v>-71244784.53</v>
+        <v>131381486.36</v>
       </c>
       <c r="AG2" t="n">
-        <v>59900143.83</v>
+        <v>25285300.85</v>
       </c>
       <c r="AH2" t="n">
-        <v>88238337.98</v>
+        <v>62115225.17</v>
       </c>
       <c r="AI2" t="n">
-        <v>26403400.5</v>
+        <v>12470823.96</v>
       </c>
       <c r="AJ2" t="n">
-        <v>61834937.48</v>
+        <v>49644401.21</v>
       </c>
       <c r="AK2" t="n">
-        <v>-513554.19</v>
+        <v>-43357949.57</v>
       </c>
       <c r="AL2" t="n">
-        <v>-4706924.97</v>
+        <v>-61267.52</v>
       </c>
       <c r="AM2" t="n">
-        <v>186608678.66</v>
+        <v>88870830.43000001</v>
       </c>
       <c r="AN2" t="n">
-        <v>114256746.75</v>
+        <v>136667738.73</v>
       </c>
       <c r="AO2" t="n">
-        <v>-68256544.04000001</v>
+        <v>-40862476.09</v>
       </c>
       <c r="AP2" t="n">
-        <v>-933121986.04</v>
+        <v>-597800065.28</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-461646162.84</v>
+        <v>-295418099.39</v>
       </c>
       <c r="AR2" t="n">
-        <v>-207200203.02</v>
+        <v>-145196398.14</v>
       </c>
       <c r="AS2" t="n">
-        <v>-264275620.18</v>
+        <v>-157185567.75</v>
       </c>
       <c r="AT2" t="n">
-        <v>1115635276.83</v>
+        <v>775330280.1</v>
       </c>
       <c r="AU2" t="n">
-        <v>88371939.19</v>
+        <v>90651991.05</v>
       </c>
       <c r="AV2" t="n">
-        <v>1027263337.64</v>
+        <v>684678289.05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-295961333.51</v>
+        <v>-146696261.93</v>
       </c>
       <c r="C3" t="n">
-        <v>-239053741.35</v>
+        <v>-502415426.64</v>
       </c>
       <c r="D3" t="n">
-        <v>599053512.72</v>
+        <v>678198998.84</v>
       </c>
       <c r="E3" t="n">
-        <v>-390700211.53</v>
+        <v>-341582523.76</v>
       </c>
       <c r="F3" t="n">
-        <v>258038745.01</v>
+        <v>287675078.59</v>
       </c>
       <c r="G3" t="n">
-        <v>287675078.59</v>
-      </c>
-      <c r="H3" t="n">
-        <v>178628.13</v>
-      </c>
+        <v>316699165.19</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>-29814961.71</v>
+        <v>-29024086.6</v>
       </c>
       <c r="J3" t="n">
-        <v>240916107.92</v>
+        <v>162235441.22</v>
       </c>
       <c r="K3" t="n">
-        <v>-60816364.47</v>
+        <v>41629250</v>
       </c>
       <c r="L3" t="n">
-        <v>-57817298.98</v>
+        <v>-55177380.98</v>
       </c>
       <c r="M3" t="n">
-        <v>359999771.37</v>
+        <v>175783572.2</v>
       </c>
       <c r="N3" t="n">
-        <v>359999771.37</v>
+        <v>175783572.2</v>
       </c>
       <c r="O3" t="n">
-        <v>-239053741.35</v>
+        <v>-502415426.64</v>
       </c>
       <c r="P3" t="n">
-        <v>599053512.72</v>
+        <v>678198998.84</v>
       </c>
       <c r="Q3" t="n">
-        <v>-365469947.65</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
+        <v>-386145789.65</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-45910000</v>
+      </c>
       <c r="S3" t="n">
-        <v>-64038235.12</v>
+        <v>1345884.11</v>
       </c>
       <c r="T3" t="n">
-        <v>1261764.88</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-65300000</v>
-      </c>
+        <v>1345884.11</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>-301431712.53</v>
+        <v>-341581673.76</v>
       </c>
       <c r="Y3" t="n">
-        <v>89268499</v>
+        <v>850</v>
       </c>
       <c r="Z3" t="n">
-        <v>-390700211.53</v>
+        <v>-341582523.76</v>
       </c>
       <c r="AA3" t="n">
-        <v>94738878.02</v>
+        <v>194886261.83</v>
       </c>
       <c r="AB3" t="n">
-        <v>-226688359.91</v>
+        <v>-46105299.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>-2932590.55</v>
+        <v>-4143425.32</v>
       </c>
       <c r="AD3" t="n">
-        <v>2430213.86</v>
+        <v>48476797.06</v>
       </c>
       <c r="AE3" t="n">
-        <v>-97219446.14</v>
+        <v>-16830711.43</v>
       </c>
       <c r="AF3" t="n">
-        <v>-128966537.08</v>
+        <v>-73607959.64</v>
       </c>
       <c r="AG3" t="n">
-        <v>34067934.2</v>
+        <v>29747080.46</v>
       </c>
       <c r="AH3" t="n">
-        <v>71550940.91</v>
+        <v>63158370.94</v>
       </c>
       <c r="AI3" t="n">
-        <v>15740447</v>
+        <v>14450060.22</v>
       </c>
       <c r="AJ3" t="n">
-        <v>55810493.91</v>
+        <v>48708310.72</v>
       </c>
       <c r="AK3" t="n">
-        <v>-1584619.4</v>
+        <v>-1269415.51</v>
       </c>
       <c r="AL3" t="n">
-        <v>-27316033.05</v>
+        <v>121579.71</v>
       </c>
       <c r="AM3" t="n">
-        <v>188818398.23</v>
+        <v>105580070.77</v>
       </c>
       <c r="AN3" t="n">
-        <v>94738878.02</v>
+        <v>194886261.83</v>
       </c>
       <c r="AO3" t="n">
-        <v>-78196126.17</v>
+        <v>-7219603.03</v>
       </c>
       <c r="AP3" t="n">
-        <v>-772458566.96</v>
+        <v>-621354128.59</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-357220984.63</v>
+        <v>-334076798.33</v>
       </c>
       <c r="AR3" t="n">
-        <v>-203311330.35</v>
+        <v>-172754387.22</v>
       </c>
       <c r="AS3" t="n">
-        <v>-211926251.98</v>
+        <v>-114522943.04</v>
       </c>
       <c r="AT3" t="n">
-        <v>945393571.15</v>
+        <v>823459993.45</v>
       </c>
       <c r="AU3" t="n">
-        <v>78027957.94</v>
+        <v>65851407.71</v>
       </c>
       <c r="AV3" t="n">
-        <v>867365613.21</v>
+        <v>757608585.74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-146696261.93</v>
+        <v>-295961333.51</v>
       </c>
       <c r="C4" t="n">
-        <v>-502415426.64</v>
+        <v>-239053741.35</v>
       </c>
       <c r="D4" t="n">
-        <v>678198998.84</v>
+        <v>599053512.72</v>
       </c>
       <c r="E4" t="n">
-        <v>-341582523.76</v>
+        <v>-390700211.53</v>
       </c>
       <c r="F4" t="n">
+        <v>258038745.01</v>
+      </c>
+      <c r="G4" t="n">
         <v>287675078.59</v>
       </c>
-      <c r="G4" t="n">
-        <v>316699165.19</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>178628.13</v>
+      </c>
       <c r="I4" t="n">
-        <v>-29024086.6</v>
+        <v>-29814961.71</v>
       </c>
       <c r="J4" t="n">
-        <v>162235441.22</v>
+        <v>240916107.92</v>
       </c>
       <c r="K4" t="n">
-        <v>41629250</v>
+        <v>-60816364.47</v>
       </c>
       <c r="L4" t="n">
-        <v>-55177380.98</v>
+        <v>-57817298.98</v>
       </c>
       <c r="M4" t="n">
-        <v>175783572.2</v>
+        <v>359999771.37</v>
       </c>
       <c r="N4" t="n">
-        <v>175783572.2</v>
+        <v>359999771.37</v>
       </c>
       <c r="O4" t="n">
-        <v>-502415426.64</v>
+        <v>-239053741.35</v>
       </c>
       <c r="P4" t="n">
-        <v>678198998.84</v>
+        <v>599053512.72</v>
       </c>
       <c r="Q4" t="n">
-        <v>-386145789.65</v>
-      </c>
-      <c r="R4" t="n">
-        <v>-45910000</v>
-      </c>
+        <v>-365469947.65</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>1345884.11</v>
+        <v>-64038235.12</v>
       </c>
       <c r="T4" t="n">
-        <v>1345884.11</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
+        <v>1261764.88</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-65300000</v>
+      </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>-341581673.76</v>
+        <v>-301431712.53</v>
       </c>
       <c r="Y4" t="n">
-        <v>850</v>
+        <v>89268499</v>
       </c>
       <c r="Z4" t="n">
-        <v>-341582523.76</v>
+        <v>-390700211.53</v>
       </c>
       <c r="AA4" t="n">
-        <v>194886261.83</v>
+        <v>94738878.02</v>
       </c>
       <c r="AB4" t="n">
-        <v>-46105299.33</v>
+        <v>-226688359.91</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4143425.32</v>
+        <v>-2932590.55</v>
       </c>
       <c r="AD4" t="n">
-        <v>48476797.06</v>
+        <v>2430213.86</v>
       </c>
       <c r="AE4" t="n">
-        <v>-16830711.43</v>
+        <v>-97219446.14</v>
       </c>
       <c r="AF4" t="n">
-        <v>-73607959.64</v>
+        <v>-128966537.08</v>
       </c>
       <c r="AG4" t="n">
-        <v>29747080.46</v>
+        <v>34067934.2</v>
       </c>
       <c r="AH4" t="n">
-        <v>63158370.94</v>
+        <v>71550940.91</v>
       </c>
       <c r="AI4" t="n">
-        <v>14450060.22</v>
+        <v>15740447</v>
       </c>
       <c r="AJ4" t="n">
-        <v>48708310.72</v>
+        <v>55810493.91</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1269415.51</v>
+        <v>-1584619.4</v>
       </c>
       <c r="AL4" t="n">
-        <v>121579.71</v>
+        <v>-27316033.05</v>
       </c>
       <c r="AM4" t="n">
-        <v>105580070.77</v>
+        <v>188818398.23</v>
       </c>
       <c r="AN4" t="n">
-        <v>194886261.83</v>
+        <v>94738878.02</v>
       </c>
       <c r="AO4" t="n">
-        <v>-7219603.03</v>
+        <v>-78196126.17</v>
       </c>
       <c r="AP4" t="n">
-        <v>-621354128.59</v>
+        <v>-772458566.96</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-334076798.33</v>
+        <v>-357220984.63</v>
       </c>
       <c r="AR4" t="n">
-        <v>-172754387.22</v>
+        <v>-203311330.35</v>
       </c>
       <c r="AS4" t="n">
-        <v>-114522943.04</v>
+        <v>-211926251.98</v>
       </c>
       <c r="AT4" t="n">
-        <v>823459993.45</v>
+        <v>945393571.15</v>
       </c>
       <c r="AU4" t="n">
-        <v>65851407.71</v>
+        <v>78027957.94</v>
       </c>
       <c r="AV4" t="n">
-        <v>757608585.74</v>
+        <v>867365613.21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-80028707.15000001</v>
+        <v>-472532455.02</v>
       </c>
       <c r="C5" t="n">
-        <v>-241501602.83</v>
+        <v>-274075297.9</v>
       </c>
       <c r="D5" t="n">
-        <v>161326781.35</v>
+        <v>850121529.92</v>
       </c>
       <c r="E5" t="n">
-        <v>-216696445.88</v>
+        <v>-586789201.77</v>
       </c>
       <c r="F5" t="n">
-        <v>316699165.19</v>
+        <v>380726679.72</v>
       </c>
       <c r="G5" t="n">
-        <v>385433489.63</v>
+        <v>258038745.01</v>
       </c>
       <c r="H5" t="n">
-        <v>-495196.68</v>
+        <v>360502.47</v>
       </c>
       <c r="I5" t="n">
-        <v>-68239127.76000001</v>
+        <v>122327432.24</v>
       </c>
       <c r="J5" t="n">
-        <v>-128693872.96</v>
+        <v>469302284.68</v>
       </c>
       <c r="K5" t="n">
-        <v>14068062.1</v>
+        <v>11335006.62</v>
       </c>
       <c r="L5" t="n">
-        <v>-62587113.58</v>
+        <v>-118078953.96</v>
       </c>
       <c r="M5" t="n">
-        <v>-80174821.48</v>
+        <v>576046232.02</v>
       </c>
       <c r="N5" t="n">
-        <v>-80174821.48</v>
+        <v>576046232.02</v>
       </c>
       <c r="O5" t="n">
-        <v>-241501602.83</v>
+        <v>-274075297.9</v>
       </c>
       <c r="P5" t="n">
-        <v>161326781.35</v>
+        <v>850121529.92</v>
       </c>
       <c r="Q5" t="n">
-        <v>-76212993.53</v>
+        <v>-461231599.19</v>
       </c>
       <c r="R5" t="n">
-        <v>-87650000</v>
+        <v>6408142.83</v>
       </c>
       <c r="S5" t="n">
-        <v>228070452.35</v>
+        <v>233348.11</v>
       </c>
       <c r="T5" t="n">
-        <v>318070453.35</v>
+        <v>326940878.77</v>
       </c>
       <c r="U5" t="n">
-        <v>-90000001</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+        <v>-326707530.66</v>
+      </c>
+      <c r="V5" t="n">
+        <v>506424.64</v>
+      </c>
+      <c r="W5" t="n">
+        <v>506424.64</v>
+      </c>
       <c r="X5" t="n">
-        <v>-216633445.88</v>
+        <v>-468379514.77</v>
       </c>
       <c r="Y5" t="n">
-        <v>63000</v>
+        <v>118409687</v>
       </c>
       <c r="Z5" t="n">
-        <v>-216696445.88</v>
+        <v>-586789201.77</v>
       </c>
       <c r="AA5" t="n">
-        <v>136667738.73</v>
+        <v>114256746.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>10035231.99</v>
+        <v>-237771444.09</v>
       </c>
       <c r="AC5" t="n">
-        <v>-6957024.73</v>
+        <v>-21975798.81</v>
       </c>
       <c r="AD5" t="n">
-        <v>-55839520.98</v>
+        <v>-16720146.87</v>
       </c>
       <c r="AE5" t="n">
-        <v>-58549708.66</v>
+        <v>-127830713.88</v>
       </c>
       <c r="AF5" t="n">
-        <v>131381486.36</v>
+        <v>-71244784.53</v>
       </c>
       <c r="AG5" t="n">
-        <v>25285300.85</v>
+        <v>59900143.83</v>
       </c>
       <c r="AH5" t="n">
-        <v>62115225.17</v>
+        <v>88238337.98</v>
       </c>
       <c r="AI5" t="n">
-        <v>12470823.96</v>
+        <v>26403400.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>49644401.21</v>
+        <v>61834937.48</v>
       </c>
       <c r="AK5" t="n">
-        <v>-43357949.57</v>
+        <v>-513554.19</v>
       </c>
       <c r="AL5" t="n">
-        <v>-61267.52</v>
+        <v>-4706924.97</v>
       </c>
       <c r="AM5" t="n">
-        <v>88870830.43000001</v>
+        <v>186608678.66</v>
       </c>
       <c r="AN5" t="n">
-        <v>136667738.73</v>
+        <v>114256746.75</v>
       </c>
       <c r="AO5" t="n">
-        <v>-40862476.09</v>
+        <v>-68256544.04000001</v>
       </c>
       <c r="AP5" t="n">
-        <v>-597800065.28</v>
+        <v>-933121986.04</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-295418099.39</v>
+        <v>-461646162.84</v>
       </c>
       <c r="AR5" t="n">
-        <v>-145196398.14</v>
+        <v>-207200203.02</v>
       </c>
       <c r="AS5" t="n">
-        <v>-157185567.75</v>
+        <v>-264275620.18</v>
       </c>
       <c r="AT5" t="n">
-        <v>775330280.1</v>
+        <v>1115635276.83</v>
       </c>
       <c r="AU5" t="n">
-        <v>90651991.05</v>
+        <v>88371939.19</v>
       </c>
       <c r="AV5" t="n">
-        <v>684678289.05</v>
+        <v>1027263337.64</v>
       </c>
     </row>
   </sheetData>
@@ -4019,197 +4019,197 @@
       </c>
       <c r="DJ1" t="inlineStr">
         <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>shortName</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
         </is>
       </c>
       <c r="EW1" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'maxAge': 1, 'name': 'Ms. Lan  Chen', 'age': 57, 'title': 'Deputy GM &amp; Director', 'yearBorn': 1968, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yongfeng  Cai', 'age': 48, 'title': 'Deputy GM, Secretary &amp; Director', 'yearBorn': 1977, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Liyun  Lin', 'age': 59, 'title': 'CFO &amp; Accounting Supervisor', 'yearBorn': 1966, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -4314,34 +4314,34 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>36</v>
+        <v>32.36</v>
       </c>
       <c r="V2" t="n">
-        <v>36</v>
+        <v>29.88</v>
       </c>
       <c r="W2" t="n">
-        <v>32.66</v>
+        <v>30.72</v>
       </c>
       <c r="X2" t="n">
-        <v>36.97</v>
+        <v>33.08</v>
       </c>
       <c r="Y2" t="n">
-        <v>36</v>
+        <v>32.36</v>
       </c>
       <c r="Z2" t="n">
-        <v>36</v>
+        <v>29.88</v>
       </c>
       <c r="AA2" t="n">
-        <v>32.66</v>
+        <v>30.72</v>
       </c>
       <c r="AB2" t="n">
-        <v>36.97</v>
+        <v>33.08</v>
       </c>
       <c r="AC2" t="n">
         <v>0.05</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="AE2" t="n">
         <v>1755129600</v>
@@ -4353,34 +4353,34 @@
         <v>0.46</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.579</v>
+        <v>0.449</v>
       </c>
       <c r="AI2" t="n">
-        <v>82.075005</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="AJ2" t="n">
-        <v>38.62353</v>
+        <v>37.10588</v>
       </c>
       <c r="AK2" t="n">
-        <v>26872083</v>
+        <v>31416990</v>
       </c>
       <c r="AL2" t="n">
-        <v>26872083</v>
+        <v>31416990</v>
       </c>
       <c r="AM2" t="n">
-        <v>26174541</v>
+        <v>24309840</v>
       </c>
       <c r="AN2" t="n">
-        <v>21166524</v>
+        <v>21229311</v>
       </c>
       <c r="AO2" t="n">
-        <v>21166524</v>
+        <v>21229311</v>
       </c>
       <c r="AP2" t="n">
-        <v>32.93</v>
+        <v>31.51</v>
       </c>
       <c r="AQ2" t="n">
-        <v>32.98</v>
+        <v>31.53</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -4389,10 +4389,10 @@
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>16728478720</v>
+        <v>16071160832</v>
       </c>
       <c r="AU2" t="n">
-        <v>16728477780</v>
+        <v>16488989977</v>
       </c>
       <c r="AV2" t="n">
         <v>12.91</v>
@@ -4407,13 +4407,13 @@
         <v>1.312867</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12.718895</v>
+        <v>12.219128</v>
       </c>
       <c r="BA2" t="n">
-        <v>39.4712</v>
+        <v>37.3358</v>
       </c>
       <c r="BB2" t="n">
-        <v>27.55405</v>
+        <v>28.55335</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
@@ -4430,7 +4430,7 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>17739538432</v>
+        <v>17117303808</v>
       </c>
       <c r="BH2" t="n">
         <v>0.15343</v>
@@ -4454,7 +4454,7 @@
         <v>3.561</v>
       </c>
       <c r="BO2" t="n">
-        <v>9.21932</v>
+        <v>8.857062000000001</v>
       </c>
       <c r="BP2" t="n">
         <v>1767139200</v>
@@ -4489,16 +4489,16 @@
         <v>1155254400</v>
       </c>
       <c r="BZ2" t="n">
-        <v>13.488</v>
+        <v>13.015</v>
       </c>
       <c r="CA2" t="n">
-        <v>64.496</v>
+        <v>62.234</v>
       </c>
       <c r="CB2" t="n">
-        <v>1.2862117</v>
+        <v>1.4796934</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.27697718</v>
+        <v>0.24487448</v>
       </c>
       <c r="CD2" t="n">
         <v>0.05</v>
@@ -4512,7 +4512,7 @@
         </is>
       </c>
       <c r="CG2" t="n">
-        <v>32.83</v>
+        <v>31.54</v>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
@@ -4615,98 +4615,86 @@
         </is>
       </c>
       <c r="DJ2" t="n">
-        <v>-8.805550999999999</v>
+        <v>31.54</v>
       </c>
       <c r="DK2" t="n">
-        <v>32.83</v>
+        <v>-0.8199997</v>
       </c>
       <c r="DL2" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>30.72 - 33.08</t>
         </is>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>Shenzhen</t>
         </is>
       </c>
       <c r="DN2" t="n">
-        <v>1780038285</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>SHZ</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>finmb_20359588</t>
-        </is>
+        <v>24309840</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>18.630001</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>1.4430674</v>
       </c>
       <c r="DQ2" t="inlineStr">
         <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
+          <t>12.91 - 49.14</t>
+        </is>
+      </c>
+      <c r="DR2" t="n">
+        <v>-17.599998</v>
       </c>
       <c r="DS2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>cn_market</t>
-        </is>
-      </c>
-      <c r="DU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>WEDGE INDUSTRIAL CO LTD</t>
-        </is>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>Wedge Industrial Co.,Ltd.</t>
-        </is>
+        <v>-0.35816032</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>147.96935</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>1619693940</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>1619693940</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0.4</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.4</v>
+        <v>0.85</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.85</v>
+        <v>-5.7957993</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-6.641197</v>
+        <v>-0.15523437</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.16825426</v>
+        <v>2.9866505</v>
       </c>
       <c r="EB2" t="n">
-        <v>5.2759514</v>
+        <v>0.10459895</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.19147643</v>
+        <v>15</v>
       </c>
       <c r="ED2" t="n">
         <v>15</v>
       </c>
-      <c r="EE2" t="n">
-        <v>15</v>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>Wedge Industrial Co., Ltd.</t>
+        </is>
       </c>
       <c r="EF2" t="inlineStr">
         <is>
-          <t>Wedge Industrial Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="EG2" t="b">
+        <v>0</v>
       </c>
       <c r="EH2" t="b">
         <v>0</v>
@@ -4717,47 +4705,59 @@
       <c r="EJ2" t="n">
         <v>758165400000</v>
       </c>
-      <c r="EK2" t="n">
-        <v>-3.1699982</v>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>32.66 - 36.97</t>
-        </is>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>Wedge Industrial Co.,Ltd.</t>
+        </is>
+      </c>
+      <c r="EL2" t="n">
+        <v>-2.5339916</v>
       </c>
       <c r="EM2" t="inlineStr">
         <is>
-          <t>Shenzhen</t>
-        </is>
-      </c>
-      <c r="EN2" t="n">
-        <v>26174541</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>19.920002</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>1.5429901</v>
-      </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>12.91 - 49.14</t>
-        </is>
-      </c>
-      <c r="ER2" t="n">
-        <v>-16.309998</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>-0.3319088</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>128.62117</v>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>finmb_20359588</t>
+        </is>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="EP2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="EQ2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="ER2" t="inlineStr">
+        <is>
+          <t>cn_market</t>
+        </is>
+      </c>
+      <c r="ES2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="ET2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="EU2" t="n">
-        <v>1619693940</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>1619693940</v>
+        <v>1782111867</v>
+      </c>
+      <c r="EV2" t="inlineStr">
+        <is>
+          <t>WEDGE INDUSTRIAL CO LTD</t>
+        </is>
       </c>
       <c r="EW2" t="inlineStr"/>
     </row>
